--- a/artfynd/A 37834-2025 artfynd.xlsx
+++ b/artfynd/A 37834-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127698051</v>
       </c>
       <c r="B2" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127698052</v>
       </c>
       <c r="B3" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127698050</v>
       </c>
       <c r="B4" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37834-2025 artfynd.xlsx
+++ b/artfynd/A 37834-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127698051</v>
       </c>
       <c r="B2" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127698052</v>
       </c>
       <c r="B3" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127698050</v>
       </c>
       <c r="B4" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37834-2025 artfynd.xlsx
+++ b/artfynd/A 37834-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127698051</v>
       </c>
       <c r="B2" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127698052</v>
       </c>
       <c r="B3" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127698050</v>
       </c>
       <c r="B4" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37834-2025 artfynd.xlsx
+++ b/artfynd/A 37834-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127698051</v>
       </c>
       <c r="B2" t="n">
-        <v>92659</v>
+        <v>92667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127698052</v>
       </c>
       <c r="B3" t="n">
-        <v>92659</v>
+        <v>92667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127698050</v>
       </c>
       <c r="B4" t="n">
-        <v>92659</v>
+        <v>92667</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37834-2025 artfynd.xlsx
+++ b/artfynd/A 37834-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127698051</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127698052</v>
       </c>
       <c r="B3" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127698050</v>
       </c>
       <c r="B4" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37834-2025 artfynd.xlsx
+++ b/artfynd/A 37834-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127698051</v>
       </c>
       <c r="B2" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127698052</v>
       </c>
       <c r="B3" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127698050</v>
       </c>
       <c r="B4" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37834-2025 artfynd.xlsx
+++ b/artfynd/A 37834-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127698051</v>
       </c>
       <c r="B2" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127698052</v>
       </c>
       <c r="B3" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127698050</v>
       </c>
       <c r="B4" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37834-2025 artfynd.xlsx
+++ b/artfynd/A 37834-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127698051</v>
       </c>
       <c r="B2" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127698052</v>
       </c>
       <c r="B3" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127698050</v>
       </c>
       <c r="B4" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37834-2025 artfynd.xlsx
+++ b/artfynd/A 37834-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127698051</v>
       </c>
       <c r="B2" t="n">
-        <v>92678</v>
+        <v>92689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127698052</v>
       </c>
       <c r="B3" t="n">
-        <v>92678</v>
+        <v>92689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127698050</v>
       </c>
       <c r="B4" t="n">
-        <v>92678</v>
+        <v>92689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
